--- a/data/dividends_info_20260516.xlsx
+++ b/data/dividends_info_20260516.xlsx
@@ -6629,14 +6629,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>IT0003865570</t>
+          <t>IT0003865588</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>2.589999914169312</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I132" t="n">
-        <v>10.03861037128218</v>
+        <v>3.023255679851103</v>
       </c>
       <c r="J132" t="n">
         <v>2</v>
@@ -9053,7 +9053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C124"/>
+  <dimension ref="A1:C114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9552,7 +9552,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9562,14 +9562,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9579,14 +9579,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -9603,7 +9603,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -9613,14 +9613,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -9630,14 +9630,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9654,7 +9654,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9664,14 +9664,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9698,14 +9698,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9722,7 +9722,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9732,14 +9732,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9749,14 +9749,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9773,7 +9773,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9783,14 +9783,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -9807,7 +9807,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9824,7 +9824,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9841,7 +9841,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9851,14 +9851,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9909,7 +9909,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9919,14 +9919,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -10011,7 +10011,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -10021,14 +10021,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10038,14 +10038,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -10062,7 +10062,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -10079,7 +10079,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -10089,48 +10089,48 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -10140,14 +10140,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -10164,12 +10164,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -10181,63 +10181,63 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -10249,63 +10249,63 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10317,24 +10317,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10344,14 +10344,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10385,7 +10385,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10402,7 +10402,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10412,53 +10412,53 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -10470,12 +10470,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -10487,12 +10487,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -10504,46 +10504,46 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -10555,12 +10555,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -10572,29 +10572,29 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -10606,46 +10606,46 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10657,12 +10657,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10674,12 +10674,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10691,12 +10691,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10708,12 +10708,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -10725,29 +10725,29 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Homizy SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -10759,12 +10759,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -10776,46 +10776,46 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -10827,12 +10827,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -10844,12 +10844,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -10861,12 +10861,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -10878,46 +10878,46 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Homizy SIIQ S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -10929,236 +10929,66 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Simone S.p.A.</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>NEUROSOFT</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>ESPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>PIQUADRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>VNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>RISANAMENTO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>RISANAMENTO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Adventure S.p.A.</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>PROMOTICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
@@ -11188,180 +11018,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Adventure S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ESPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NEUROSOFT</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>PIQUADRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PROMOTICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RISANAMENTO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RISANAMENTO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>VNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>